--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30524"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F10A8DCD-643D-4C18-94D9-DD26051FE161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1339" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6F3CF3A-D0D8-4077-8C76-9C30B5420B9F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MPR Masterfile" sheetId="1" r:id="rId1"/>
@@ -859,9 +859,6 @@
     <t>Clear to build material avaialbility</t>
   </si>
   <si>
-    <t>OOH%</t>
-  </si>
-  <si>
     <t>B&amp;B to meet sales AOP</t>
   </si>
   <si>
@@ -1020,21 +1017,6 @@
 (Sec 7 - IQ-PSW signoff)  - SVAL</t>
   </si>
   <si>
-    <t>LCM ::SICR Inflow  vs Outflow</t>
-  </si>
-  <si>
-    <t>SICR burndown [ outflow / inflow &gt; 1 ]</t>
-  </si>
-  <si>
-    <t>&gt;=1</t>
-  </si>
-  <si>
-    <t>LCM :: Production Delay due to delay in CR's</t>
-  </si>
-  <si>
-    <t>Production stops due to delay in CR/SICR</t>
-  </si>
-  <si>
     <t>Critical &amp; MLD Milestone Delivery On-Time (%)</t>
   </si>
   <si>
@@ -1362,6 +1344,24 @@
   </si>
   <si>
     <t>Order Intake CS(Growth)</t>
+  </si>
+  <si>
+    <t>LCM :: Production Delay due to delay in CR's</t>
+  </si>
+  <si>
+    <t>Production stops due to delay in CR/SICR</t>
+  </si>
+  <si>
+    <t>SICR burndown [ outflow / inflow &gt; 1 ]</t>
+  </si>
+  <si>
+    <t>&gt;=1</t>
+  </si>
+  <si>
+    <t>LCM ::SICR Inflow  vs Outflow</t>
+  </si>
+  <si>
+    <t>OOH%</t>
   </si>
 </sst>
 </file>
@@ -1373,7 +1373,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1546,7 +1546,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1585,6 +1585,10 @@
     <xf numFmtId="2" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2477,35 +2481,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y59"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="55.28515625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" hidden="1" customWidth="1"/>
-    <col min="5" max="6" width="10.7109375" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="8.7109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" hidden="1" customWidth="1"/>
-    <col min="11" max="13" width="8.7109375" customWidth="1"/>
-    <col min="14" max="14" width="8.140625" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="55.26953125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" hidden="1" customWidth="1"/>
+    <col min="5" max="6" width="10.7265625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="15.54296875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="8.7265625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7265625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="15.1796875" hidden="1" customWidth="1"/>
+    <col min="11" max="13" width="8.7265625" customWidth="1"/>
+    <col min="14" max="14" width="8.1796875" customWidth="1"/>
     <col min="15" max="15" width="8" customWidth="1"/>
-    <col min="16" max="17" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" customWidth="1"/>
+    <col min="16" max="17" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15.95" customHeight="1">
+    <row r="1" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -2576,7 +2580,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -2633,7 +2637,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -2690,7 +2694,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -2745,7 +2749,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -2802,7 +2806,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -2855,7 +2859,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -2908,7 +2912,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -2968,7 +2972,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -3028,12 +3032,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -3104,7 +3108,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>45</v>
       </c>
@@ -3162,7 +3166,7 @@
       </c>
       <c r="Y15" s="2"/>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -3220,7 +3224,7 @@
       </c>
       <c r="Y16" s="2"/>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -3278,7 +3282,7 @@
       </c>
       <c r="Y17" s="2"/>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -3336,7 +3340,7 @@
       </c>
       <c r="Y18" s="2"/>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>51</v>
       </c>
@@ -3400,7 +3404,7 @@
       </c>
       <c r="Y19" s="2"/>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -3464,12 +3468,12 @@
       </c>
       <c r="Y20" s="2"/>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -3540,7 +3544,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -3597,7 +3601,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -3654,7 +3658,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -3711,7 +3715,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -3768,7 +3772,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>62</v>
       </c>
@@ -3825,7 +3829,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -3882,7 +3886,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>64</v>
       </c>
@@ -3945,7 +3949,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>64</v>
       </c>
@@ -4008,12 +4012,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>2</v>
       </c>
@@ -4084,7 +4088,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -4141,7 +4145,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -4198,7 +4202,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>70</v>
       </c>
@@ -4249,7 +4253,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -4300,7 +4304,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:23">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>74</v>
       </c>
@@ -4361,7 +4365,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:23">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>74</v>
       </c>
@@ -4422,7 +4426,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:23">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>76</v>
       </c>
@@ -4481,7 +4485,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:23">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>76</v>
       </c>
@@ -4540,12 +4544,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:23">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="42" spans="1:23">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>2</v>
       </c>
@@ -4616,7 +4620,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:23">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>79</v>
       </c>
@@ -4667,7 +4671,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:23">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>79</v>
       </c>
@@ -4718,7 +4722,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:23">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>81</v>
       </c>
@@ -4775,7 +4779,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:23">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>81</v>
       </c>
@@ -4832,7 +4836,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:23">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>84</v>
       </c>
@@ -4889,7 +4893,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="1:23">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>84</v>
       </c>
@@ -4946,7 +4950,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:23">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>85</v>
       </c>
@@ -5003,7 +5007,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:23">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>85</v>
       </c>
@@ -5060,7 +5064,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="51" spans="1:23">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>86</v>
       </c>
@@ -5117,7 +5121,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:23">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>86</v>
       </c>
@@ -5174,12 +5178,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:23">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="55" spans="1:23">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>2</v>
       </c>
@@ -5250,7 +5254,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="1:23">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>89</v>
       </c>
@@ -5295,7 +5299,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:23">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>89</v>
       </c>
@@ -5340,7 +5344,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="58" spans="1:23">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -5383,7 +5387,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="59" spans="1:23">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>91</v>
       </c>
@@ -5443,33 +5447,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:V200"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="5" width="43.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" customWidth="1"/>
-    <col min="7" max="11" width="43.42578125" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="35.5703125" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.85546875" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" customWidth="1"/>
-    <col min="17" max="19" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="5" width="43.36328125" customWidth="1"/>
+    <col min="6" max="6" width="15.36328125" customWidth="1"/>
+    <col min="7" max="11" width="43.36328125" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="35.6328125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="11.453125" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.81640625" customWidth="1"/>
+    <col min="16" max="16" width="11.453125" customWidth="1"/>
+    <col min="17" max="19" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="18.600000000000001" customHeight="1">
+    <row r="1" spans="1:22" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="11" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>97</v>
       </c>
@@ -5537,7 +5541,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>114</v>
       </c>
@@ -5597,7 +5601,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>114</v>
       </c>
@@ -5640,7 +5644,7 @@
       <c r="N6" s="4">
         <v>0.3</v>
       </c>
-      <c r="O6" s="4">
+      <c r="O6" s="39">
         <v>0.4</v>
       </c>
       <c r="P6" s="4">
@@ -5657,7 +5661,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>120</v>
       </c>
@@ -5700,7 +5704,7 @@
       <c r="N7">
         <v>4</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="38">
         <v>4</v>
       </c>
       <c r="P7">
@@ -5713,7 +5717,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>120</v>
       </c>
@@ -5756,7 +5760,7 @@
       <c r="N8">
         <v>4</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="38">
         <v>4</v>
       </c>
       <c r="P8">
@@ -5769,7 +5773,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>123</v>
       </c>
@@ -5812,7 +5816,7 @@
       <c r="N9">
         <v>0</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="38">
         <v>0</v>
       </c>
       <c r="P9">
@@ -5825,7 +5829,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>123</v>
       </c>
@@ -5868,7 +5872,7 @@
       <c r="N10">
         <v>0</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="38">
         <v>0</v>
       </c>
       <c r="P10">
@@ -5881,7 +5885,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -5924,7 +5928,7 @@
       <c r="N11" s="2">
         <v>0.9</v>
       </c>
-      <c r="O11" s="2">
+      <c r="O11" s="40">
         <v>0.9</v>
       </c>
       <c r="P11" s="2">
@@ -5941,7 +5945,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>126</v>
       </c>
@@ -5984,7 +5988,7 @@
       <c r="N12" s="2">
         <v>0</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12" s="40">
         <v>1</v>
       </c>
       <c r="P12" s="2">
@@ -6001,7 +6005,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -6044,7 +6048,7 @@
       <c r="N13" s="2">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="O13" s="3">
+      <c r="O13" s="41">
         <v>0.06</v>
       </c>
       <c r="P13" s="3">
@@ -6061,7 +6065,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -6104,7 +6108,7 @@
       <c r="N14" s="3">
         <v>0.03</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="41">
         <v>0.03</v>
       </c>
       <c r="P14" s="3">
@@ -6121,7 +6125,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>132</v>
       </c>
@@ -6181,7 +6185,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>132</v>
       </c>
@@ -6237,7 +6241,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>134</v>
       </c>
@@ -6297,7 +6301,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>134</v>
       </c>
@@ -6353,7 +6357,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>136</v>
       </c>
@@ -6413,7 +6417,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>136</v>
       </c>
@@ -6469,7 +6473,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>138</v>
       </c>
@@ -6525,7 +6529,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>138</v>
       </c>
@@ -6581,12 +6585,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>97</v>
       </c>
@@ -6654,7 +6658,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>141</v>
       </c>
@@ -6714,7 +6718,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>141</v>
       </c>
@@ -6774,7 +6778,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>143</v>
       </c>
@@ -6834,7 +6838,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>143</v>
       </c>
@@ -6894,7 +6898,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>145</v>
       </c>
@@ -6954,7 +6958,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>145</v>
       </c>
@@ -7014,7 +7018,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>147</v>
       </c>
@@ -7074,7 +7078,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>147</v>
       </c>
@@ -7134,7 +7138,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>149</v>
       </c>
@@ -7194,7 +7198,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>149</v>
       </c>
@@ -7254,7 +7258,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>151</v>
       </c>
@@ -7298,7 +7302,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>151</v>
       </c>
@@ -7342,7 +7346,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>153</v>
       </c>
@@ -7402,7 +7406,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>153</v>
       </c>
@@ -7462,13 +7466,13 @@
         <v>129</v>
       </c>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>155</v>
       </c>
       <c r="V39" s="12"/>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>97</v>
       </c>
@@ -7536,7 +7540,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>156</v>
       </c>
@@ -7594,7 +7598,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="42" spans="1:22">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>156</v>
       </c>
@@ -7652,7 +7656,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="43" spans="1:22">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>158</v>
       </c>
@@ -7705,7 +7709,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>158</v>
       </c>
@@ -7758,7 +7762,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>161</v>
       </c>
@@ -7818,7 +7822,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>161</v>
       </c>
@@ -7878,18 +7882,18 @@
         <v>118</v>
       </c>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
+        <v>326</v>
+      </c>
+      <c r="B47" t="s">
         <v>163</v>
-      </c>
-      <c r="B47" t="s">
-        <v>164</v>
       </c>
       <c r="C47" t="s">
         <v>116</v>
       </c>
       <c r="D47" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E47" t="s">
         <v>60</v>
@@ -7928,16 +7932,16 @@
         <v>0.95</v>
       </c>
       <c r="Q47" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R47" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S47" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T47" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U47" t="s">
         <v>32</v>
@@ -7946,18 +7950,18 @@
         <v>118</v>
       </c>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
+        <v>326</v>
+      </c>
+      <c r="B48" t="s">
         <v>163</v>
-      </c>
-      <c r="B48" t="s">
-        <v>164</v>
       </c>
       <c r="C48" t="s">
         <v>116</v>
       </c>
       <c r="D48" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E48" t="s">
         <v>60</v>
@@ -7996,16 +8000,16 @@
         <v>0.71</v>
       </c>
       <c r="Q48" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R48" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S48" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T48" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U48" t="s">
         <v>32</v>
@@ -8014,18 +8018,18 @@
         <v>118</v>
       </c>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
+        <v>166</v>
+      </c>
+      <c r="B49" t="s">
         <v>167</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>168</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>169</v>
-      </c>
-      <c r="D49" t="s">
-        <v>170</v>
       </c>
       <c r="E49" t="s">
         <v>60</v>
@@ -8072,18 +8076,18 @@
         <v>118</v>
       </c>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
+        <v>166</v>
+      </c>
+      <c r="B50" t="s">
         <v>167</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>168</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>169</v>
-      </c>
-      <c r="D50" t="s">
-        <v>170</v>
       </c>
       <c r="E50" t="s">
         <v>60</v>
@@ -8130,12 +8134,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
+        <v>170</v>
+      </c>
+      <c r="B51" t="s">
         <v>171</v>
-      </c>
-      <c r="B51" t="s">
-        <v>172</v>
       </c>
       <c r="C51" t="s">
         <v>122</v>
@@ -8188,12 +8192,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>170</v>
+      </c>
+      <c r="B52" t="s">
         <v>171</v>
-      </c>
-      <c r="B52" t="s">
-        <v>172</v>
       </c>
       <c r="C52" t="s">
         <v>122</v>
@@ -8246,18 +8250,18 @@
         <v>118</v>
       </c>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
+        <v>172</v>
+      </c>
+      <c r="B53" t="s">
         <v>173</v>
-      </c>
-      <c r="B53" t="s">
-        <v>174</v>
       </c>
       <c r="C53" t="s">
         <v>116</v>
       </c>
       <c r="D53" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E53" t="s">
         <v>60</v>
@@ -8304,18 +8308,18 @@
         <v>129</v>
       </c>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
+        <v>172</v>
+      </c>
+      <c r="B54" t="s">
         <v>173</v>
-      </c>
-      <c r="B54" t="s">
-        <v>174</v>
       </c>
       <c r="C54" t="s">
         <v>116</v>
       </c>
       <c r="D54" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E54" t="s">
         <v>60</v>
@@ -8362,12 +8366,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>176</v>
+      </c>
+      <c r="B55" t="s">
         <v>177</v>
-      </c>
-      <c r="B55" t="s">
-        <v>178</v>
       </c>
       <c r="C55" t="s">
         <v>116</v>
@@ -8420,12 +8424,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
+        <v>176</v>
+      </c>
+      <c r="B56" t="s">
         <v>177</v>
-      </c>
-      <c r="B56" t="s">
-        <v>178</v>
       </c>
       <c r="C56" t="s">
         <v>116</v>
@@ -8478,18 +8482,18 @@
         <v>129</v>
       </c>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>178</v>
+      </c>
+      <c r="B57" t="s">
         <v>179</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
+        <v>168</v>
+      </c>
+      <c r="D57" t="s">
         <v>180</v>
-      </c>
-      <c r="C57" t="s">
-        <v>169</v>
-      </c>
-      <c r="D57" t="s">
-        <v>181</v>
       </c>
       <c r="E57" t="s">
         <v>29</v>
@@ -8536,15 +8540,15 @@
         <v>129</v>
       </c>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
+        <v>178</v>
+      </c>
+      <c r="B58" t="s">
         <v>179</v>
       </c>
-      <c r="B58" t="s">
-        <v>180</v>
-      </c>
       <c r="C58" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E58" t="s">
         <v>29</v>
@@ -8591,12 +8595,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
+        <v>181</v>
+      </c>
+      <c r="B59" t="s">
         <v>182</v>
-      </c>
-      <c r="B59" t="s">
-        <v>183</v>
       </c>
       <c r="C59" t="s">
         <v>128</v>
@@ -8614,7 +8618,7 @@
         <v>30</v>
       </c>
       <c r="H59" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I59">
         <v>13</v>
@@ -8644,12 +8648,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="60" spans="1:22">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
+        <v>181</v>
+      </c>
+      <c r="B60" t="s">
         <v>182</v>
-      </c>
-      <c r="B60" t="s">
-        <v>183</v>
       </c>
       <c r="C60" t="s">
         <v>128</v>
@@ -8697,12 +8701,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="61" spans="1:22">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
+        <v>184</v>
+      </c>
+      <c r="B61" t="s">
         <v>185</v>
-      </c>
-      <c r="B61" t="s">
-        <v>186</v>
       </c>
       <c r="C61" t="s">
         <v>128</v>
@@ -8755,12 +8759,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="62" spans="1:22">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
+        <v>184</v>
+      </c>
+      <c r="B62" t="s">
         <v>185</v>
-      </c>
-      <c r="B62" t="s">
-        <v>186</v>
       </c>
       <c r="C62" t="s">
         <v>128</v>
@@ -8813,12 +8817,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="63" spans="1:22">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
+        <v>186</v>
+      </c>
+      <c r="B63" t="s">
         <v>187</v>
-      </c>
-      <c r="B63" t="s">
-        <v>188</v>
       </c>
       <c r="C63" t="s">
         <v>128</v>
@@ -8871,12 +8875,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="64" spans="1:22">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
+        <v>186</v>
+      </c>
+      <c r="B64" t="s">
         <v>187</v>
-      </c>
-      <c r="B64" t="s">
-        <v>188</v>
       </c>
       <c r="C64" t="s">
         <v>128</v>
@@ -8929,12 +8933,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="65" spans="1:22">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
+        <v>188</v>
+      </c>
+      <c r="B65" t="s">
         <v>189</v>
-      </c>
-      <c r="B65" t="s">
-        <v>190</v>
       </c>
       <c r="C65" t="s">
         <v>128</v>
@@ -8987,12 +8991,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:22">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
+        <v>188</v>
+      </c>
+      <c r="B66" t="s">
         <v>189</v>
-      </c>
-      <c r="B66" t="s">
-        <v>190</v>
       </c>
       <c r="C66" t="s">
         <v>128</v>
@@ -9045,15 +9049,15 @@
         <v>129</v>
       </c>
     </row>
-    <row r="67" spans="1:22" ht="14.1" customHeight="1">
+    <row r="67" spans="1:22" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
+        <v>190</v>
+      </c>
+      <c r="B67" t="s">
         <v>191</v>
       </c>
-      <c r="B67" t="s">
-        <v>192</v>
-      </c>
       <c r="C67" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D67">
         <v>0.03</v>
@@ -9098,15 +9102,15 @@
         <v>129</v>
       </c>
     </row>
-    <row r="68" spans="1:22">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
+        <v>190</v>
+      </c>
+      <c r="B68" t="s">
         <v>191</v>
       </c>
-      <c r="B68" t="s">
-        <v>192</v>
-      </c>
       <c r="C68" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D68">
         <v>0.03</v>
@@ -9151,12 +9155,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="69" spans="1:22">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
+        <v>192</v>
+      </c>
+      <c r="B69" t="s">
         <v>193</v>
-      </c>
-      <c r="B69" t="s">
-        <v>194</v>
       </c>
       <c r="C69" t="s">
         <v>128</v>
@@ -9209,12 +9213,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="70" spans="1:22">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
+        <v>192</v>
+      </c>
+      <c r="B70" t="s">
         <v>193</v>
-      </c>
-      <c r="B70" t="s">
-        <v>194</v>
       </c>
       <c r="C70" t="s">
         <v>128</v>
@@ -9267,12 +9271,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="71" spans="1:22">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
+        <v>194</v>
+      </c>
+      <c r="B71" t="s">
         <v>195</v>
-      </c>
-      <c r="B71" t="s">
-        <v>196</v>
       </c>
       <c r="C71" t="s">
         <v>122</v>
@@ -9320,12 +9324,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="72" spans="1:22">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
+        <v>194</v>
+      </c>
+      <c r="B72" t="s">
         <v>195</v>
-      </c>
-      <c r="B72" t="s">
-        <v>196</v>
       </c>
       <c r="C72" t="s">
         <v>122</v>
@@ -9373,12 +9377,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:22">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
+        <v>196</v>
+      </c>
+      <c r="B73" t="s">
         <v>197</v>
-      </c>
-      <c r="B73" t="s">
-        <v>198</v>
       </c>
       <c r="C73" t="s">
         <v>122</v>
@@ -9426,12 +9430,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="74" spans="1:22">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
+        <v>196</v>
+      </c>
+      <c r="B74" t="s">
         <v>197</v>
-      </c>
-      <c r="B74" t="s">
-        <v>198</v>
       </c>
       <c r="C74" t="s">
         <v>122</v>
@@ -9467,9 +9471,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="75" spans="1:22">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B75" t="s">
         <v>162</v>
@@ -9525,9 +9529,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="76" spans="1:22">
+    <row r="76" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B76" t="s">
         <v>162</v>
@@ -9583,18 +9587,18 @@
         <v>118</v>
       </c>
     </row>
-    <row r="77" spans="1:22">
+    <row r="77" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
+        <v>199</v>
+      </c>
+      <c r="B77" t="s">
         <v>200</v>
-      </c>
-      <c r="B77" t="s">
-        <v>201</v>
       </c>
       <c r="C77" t="s">
         <v>122</v>
       </c>
       <c r="D77" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E77" t="s">
         <v>29</v>
@@ -9636,18 +9640,18 @@
         <v>129</v>
       </c>
     </row>
-    <row r="78" spans="1:22">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
+        <v>199</v>
+      </c>
+      <c r="B78" t="s">
         <v>200</v>
-      </c>
-      <c r="B78" t="s">
-        <v>201</v>
       </c>
       <c r="C78" t="s">
         <v>122</v>
       </c>
       <c r="D78" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E78" t="s">
         <v>29</v>
@@ -9689,9 +9693,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="79" spans="1:22">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B79" t="s">
         <v>162</v>
@@ -9747,9 +9751,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="80" spans="1:22">
+    <row r="80" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B80" t="s">
         <v>162</v>
@@ -9805,12 +9809,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="81" spans="1:22">
+    <row r="81" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
+        <v>203</v>
+      </c>
+      <c r="B81" t="s">
         <v>204</v>
-      </c>
-      <c r="B81" t="s">
-        <v>205</v>
       </c>
       <c r="C81" t="s">
         <v>125</v>
@@ -9863,12 +9867,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="82" spans="1:22">
+    <row r="82" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
+        <v>203</v>
+      </c>
+      <c r="B82" t="s">
         <v>204</v>
-      </c>
-      <c r="B82" t="s">
-        <v>205</v>
       </c>
       <c r="C82" t="s">
         <v>125</v>
@@ -9909,12 +9913,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="83" spans="1:22">
+    <row r="83" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="84" spans="1:22">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>97</v>
       </c>
@@ -9982,12 +9986,12 @@
         <v>113</v>
       </c>
     </row>
-    <row r="85" spans="1:22">
+    <row r="85" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
+        <v>206</v>
+      </c>
+      <c r="B85" t="s">
         <v>207</v>
-      </c>
-      <c r="B85" t="s">
-        <v>208</v>
       </c>
       <c r="C85" t="s">
         <v>128</v>
@@ -10038,12 +10042,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="86" spans="1:22">
+    <row r="86" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
+        <v>206</v>
+      </c>
+      <c r="B86" t="s">
         <v>207</v>
-      </c>
-      <c r="B86" t="s">
-        <v>208</v>
       </c>
       <c r="C86" t="s">
         <v>128</v>
@@ -10094,12 +10098,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="87" spans="1:22">
+    <row r="87" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
+        <v>208</v>
+      </c>
+      <c r="B87" t="s">
         <v>209</v>
-      </c>
-      <c r="B87" t="s">
-        <v>210</v>
       </c>
       <c r="C87" t="s">
         <v>128</v>
@@ -10150,12 +10154,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="88" spans="1:22">
+    <row r="88" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
+        <v>208</v>
+      </c>
+      <c r="B88" t="s">
         <v>209</v>
-      </c>
-      <c r="B88" t="s">
-        <v>210</v>
       </c>
       <c r="C88" t="s">
         <v>128</v>
@@ -10206,12 +10210,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="89" spans="1:22">
+    <row r="89" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
+        <v>210</v>
+      </c>
+      <c r="B89" t="s">
         <v>211</v>
-      </c>
-      <c r="B89" t="s">
-        <v>212</v>
       </c>
       <c r="C89" t="s">
         <v>128</v>
@@ -10262,12 +10266,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="90" spans="1:22">
+    <row r="90" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
+        <v>210</v>
+      </c>
+      <c r="B90" t="s">
         <v>211</v>
-      </c>
-      <c r="B90" t="s">
-        <v>212</v>
       </c>
       <c r="C90" t="s">
         <v>128</v>
@@ -10318,18 +10322,18 @@
         <v>118</v>
       </c>
     </row>
-    <row r="91" spans="1:22">
+    <row r="91" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>213</v>
+        <v>325</v>
       </c>
       <c r="B91" t="s">
-        <v>214</v>
+        <v>323</v>
       </c>
       <c r="C91" t="s">
         <v>128</v>
       </c>
       <c r="D91" t="s">
-        <v>215</v>
+        <v>324</v>
       </c>
       <c r="E91" t="s">
         <v>29</v>
@@ -10366,18 +10370,18 @@
       </c>
       <c r="V91" s="19"/>
     </row>
-    <row r="92" spans="1:22">
+    <row r="92" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>213</v>
+        <v>325</v>
       </c>
       <c r="B92" t="s">
-        <v>214</v>
+        <v>323</v>
       </c>
       <c r="C92" t="s">
         <v>128</v>
       </c>
       <c r="D92" t="s">
-        <v>215</v>
+        <v>324</v>
       </c>
       <c r="E92" t="s">
         <v>29</v>
@@ -10414,12 +10418,12 @@
       </c>
       <c r="V92" s="19"/>
     </row>
-    <row r="93" spans="1:22">
+    <row r="93" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>216</v>
+        <v>321</v>
       </c>
       <c r="B93" t="s">
-        <v>217</v>
+        <v>322</v>
       </c>
       <c r="C93" t="s">
         <v>128</v>
@@ -10462,12 +10466,12 @@
       </c>
       <c r="V93" s="19"/>
     </row>
-    <row r="94" spans="1:22">
+    <row r="94" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>216</v>
+        <v>321</v>
       </c>
       <c r="B94" t="s">
-        <v>217</v>
+        <v>322</v>
       </c>
       <c r="C94" t="s">
         <v>128</v>
@@ -10510,12 +10514,12 @@
       </c>
       <c r="V94" s="19"/>
     </row>
-    <row r="95" spans="1:22">
+    <row r="95" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B95" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C95" t="s">
         <v>128</v>
@@ -10568,12 +10572,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="96" spans="1:22">
+    <row r="96" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B96" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C96" t="s">
         <v>128</v>
@@ -10626,12 +10630,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="97" spans="1:22">
+    <row r="97" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B97" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C97" t="s">
         <v>128</v>
@@ -10682,12 +10686,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="98" spans="1:22">
+    <row r="98" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B98" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C98" t="s">
         <v>128</v>
@@ -10738,12 +10742,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="99" spans="1:22">
+    <row r="99" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B99" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C99" t="s">
         <v>128</v>
@@ -10794,12 +10798,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="100" spans="1:22">
+    <row r="100" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B100" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C100" t="s">
         <v>128</v>
@@ -10850,12 +10854,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="101" spans="1:22">
+    <row r="101" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>76</v>
       </c>
       <c r="B101" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C101" t="s">
         <v>128</v>
@@ -10906,12 +10910,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="102" spans="1:22">
+    <row r="102" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>76</v>
       </c>
       <c r="B102" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C102" t="s">
         <v>128</v>
@@ -10962,12 +10966,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="103" spans="1:22">
+    <row r="103" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="104" spans="1:22">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="104" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>97</v>
       </c>
@@ -11035,12 +11039,12 @@
         <v>113</v>
       </c>
     </row>
-    <row r="105" spans="1:22">
+    <row r="105" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B105" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C105" t="s">
         <v>128</v>
@@ -11093,12 +11097,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="106" spans="1:22">
+    <row r="106" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B106" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C106" t="s">
         <v>128</v>
@@ -11113,7 +11117,7 @@
         <v>36</v>
       </c>
       <c r="G106" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="H106" t="s">
         <v>119</v>
@@ -11151,12 +11155,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="107" spans="1:22">
+    <row r="107" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B107" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C107" t="s">
         <v>128</v>
@@ -11204,12 +11208,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="108" spans="1:22">
+    <row r="108" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B108" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C108" t="s">
         <v>128</v>
@@ -11257,12 +11261,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="109" spans="1:22">
+    <row r="109" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B109" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C109" t="s">
         <v>128</v>
@@ -11310,12 +11314,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="110" spans="1:22">
+    <row r="110" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B110" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C110" t="s">
         <v>128</v>
@@ -11363,12 +11367,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="111" spans="1:22">
+    <row r="111" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B111" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C111" t="s">
         <v>128</v>
@@ -11421,12 +11425,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="112" spans="1:22">
+    <row r="112" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B112" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C112" t="s">
         <v>128</v>
@@ -11479,12 +11483,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="113" spans="1:22">
+    <row r="113" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B113" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C113" t="s">
         <v>128</v>
@@ -11537,12 +11541,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="114" spans="1:22">
+    <row r="114" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B114" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C114" t="s">
         <v>128</v>
@@ -11591,12 +11595,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="115" spans="1:22">
+    <row r="115" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B115" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C115" t="s">
         <v>128</v>
@@ -11645,12 +11649,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="116" spans="1:22">
+    <row r="116" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B116" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C116" t="s">
         <v>128</v>
@@ -11699,12 +11703,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="117" spans="1:22">
+    <row r="117" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="118" spans="1:22">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="118" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>97</v>
       </c>
@@ -11772,12 +11776,12 @@
         <v>113</v>
       </c>
     </row>
-    <row r="119" spans="1:22">
+    <row r="119" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B119" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C119" t="s">
         <v>128</v>
@@ -11830,12 +11834,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:22">
+    <row r="120" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B120" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C120" t="s">
         <v>128</v>
@@ -11888,12 +11892,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="121" spans="1:22">
+    <row r="121" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B121" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C121" t="s">
         <v>128</v>
@@ -11946,12 +11950,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="122" spans="1:22">
+    <row r="122" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B122" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C122" t="s">
         <v>128</v>
@@ -12004,12 +12008,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="123" spans="1:22">
+    <row r="123" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B123" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C123" t="s">
         <v>128</v>
@@ -12057,12 +12061,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="124" spans="1:22">
+    <row r="124" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B124" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C124" t="s">
         <v>128</v>
@@ -12110,12 +12114,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="125" spans="1:22">
+    <row r="125" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B125" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C125" t="s">
         <v>122</v>
@@ -12163,12 +12167,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="126" spans="1:22">
+    <row r="126" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B126" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C126" t="s">
         <v>122</v>
@@ -12216,12 +12220,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="127" spans="1:22">
+    <row r="127" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B127" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C127" t="s">
         <v>128</v>
@@ -12274,12 +12278,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="128" spans="1:22">
+    <row r="128" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B128" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C128" t="s">
         <v>128</v>
@@ -12332,12 +12336,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="129" spans="1:22">
+    <row r="129" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B129" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C129" t="s">
         <v>128</v>
@@ -12390,12 +12394,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="130" spans="1:22">
+    <row r="130" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B130" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C130" t="s">
         <v>128</v>
@@ -12448,12 +12452,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="131" spans="1:22">
+    <row r="131" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B131" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C131" t="s">
         <v>122</v>
@@ -12506,12 +12510,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="132" spans="1:22">
+    <row r="132" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B132" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C132" t="s">
         <v>122</v>
@@ -12564,12 +12568,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="133" spans="1:22">
+    <row r="133" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B133" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C133" t="s">
         <v>128</v>
@@ -12612,12 +12616,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="134" spans="1:22">
+    <row r="134" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B134" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C134" t="s">
         <v>128</v>
@@ -12660,12 +12664,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="135" spans="1:22">
+    <row r="135" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B135" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C135" t="s">
         <v>128</v>
@@ -12718,12 +12722,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="136" spans="1:22">
+    <row r="136" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B136" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C136" t="s">
         <v>128</v>
@@ -12776,12 +12780,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="137" spans="1:22">
+    <row r="137" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B137" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C137" t="s">
         <v>128</v>
@@ -12834,12 +12838,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="138" spans="1:22">
+    <row r="138" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B138" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C138" t="s">
         <v>128</v>
@@ -12892,12 +12896,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="139" spans="1:22">
+    <row r="139" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="140" spans="1:22">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="140" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>97</v>
       </c>
@@ -12965,18 +12969,18 @@
         <v>113</v>
       </c>
     </row>
-    <row r="141" spans="1:22">
+    <row r="141" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B141" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C141" t="s">
         <v>128</v>
       </c>
       <c r="D141" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="E141" t="s">
         <v>39</v>
@@ -13021,18 +13025,18 @@
         <v>118</v>
       </c>
     </row>
-    <row r="142" spans="1:22">
+    <row r="142" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B142" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C142" t="s">
         <v>128</v>
       </c>
       <c r="D142" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="E142" t="s">
         <v>39</v>
@@ -13077,12 +13081,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="143" spans="1:22">
+    <row r="143" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B143" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C143" t="s">
         <v>128</v>
@@ -13130,12 +13134,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="144" spans="1:22">
+    <row r="144" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B144" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C144" t="s">
         <v>128</v>
@@ -13183,12 +13187,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="145" spans="1:22">
+    <row r="145" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B145" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C145" t="s">
         <v>128</v>
@@ -13241,12 +13245,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="146" spans="1:22">
+    <row r="146" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B146" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C146" t="s">
         <v>128</v>
@@ -13299,12 +13303,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="147" spans="1:22">
+    <row r="147" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B147" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C147" t="s">
         <v>128</v>
@@ -13357,12 +13361,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="148" spans="1:22">
+    <row r="148" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B148" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C148" t="s">
         <v>128</v>
@@ -13407,12 +13411,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="149" spans="1:22">
+    <row r="149" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B149" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C149" t="s">
         <v>128</v>
@@ -13465,12 +13469,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="150" spans="1:22">
+    <row r="150" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B150" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C150" t="s">
         <v>128</v>
@@ -13523,12 +13527,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="151" spans="1:22">
+    <row r="151" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B151" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C151" t="s">
         <v>128</v>
@@ -13581,12 +13585,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="152" spans="1:22">
+    <row r="152" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B152" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C152" t="s">
         <v>128</v>
@@ -13639,12 +13643,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="153" spans="1:22">
+    <row r="153" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B153" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C153" t="s">
         <v>125</v>
@@ -13695,12 +13699,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="154" spans="1:22">
+    <row r="154" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B154" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C154" t="s">
         <v>125</v>
@@ -13745,18 +13749,18 @@
         <v>129</v>
       </c>
     </row>
-    <row r="155" spans="1:22">
+    <row r="155" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B155" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C155" t="s">
         <v>116</v>
       </c>
       <c r="D155" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E155" t="s">
         <v>60</v>
@@ -13793,7 +13797,7 @@
       </c>
       <c r="P155" s="24"/>
       <c r="Q155" s="5" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="R155" s="24"/>
       <c r="S155" s="24"/>
@@ -13805,18 +13809,18 @@
         <v>129</v>
       </c>
     </row>
-    <row r="156" spans="1:22">
+    <row r="156" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B156" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C156" t="s">
         <v>116</v>
       </c>
       <c r="D156" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="E156" t="s">
         <v>60</v>
@@ -13863,12 +13867,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="157" spans="1:22">
+    <row r="157" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B157" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C157" t="s">
         <v>128</v>
@@ -13919,12 +13923,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="158" spans="1:22">
+    <row r="158" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B158" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C158" t="s">
         <v>128</v>
@@ -13971,12 +13975,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="159" spans="1:22">
+    <row r="159" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="160" spans="1:22">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="160" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>97</v>
       </c>
@@ -14044,12 +14048,12 @@
         <v>113</v>
       </c>
     </row>
-    <row r="161" spans="1:22">
+    <row r="161" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B161" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C161" t="s">
         <v>128</v>
@@ -14100,12 +14104,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="162" spans="1:22">
+    <row r="162" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B162" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C162" t="s">
         <v>128</v>
@@ -14156,12 +14160,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="163" spans="1:22">
+    <row r="163" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B163" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C163" t="s">
         <v>125</v>
@@ -14216,12 +14220,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="164" spans="1:22">
+    <row r="164" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B164" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C164" t="s">
         <v>125</v>
@@ -14272,12 +14276,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="165" spans="1:22">
+    <row r="165" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B165" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C165" t="s">
         <v>125</v>
@@ -14332,12 +14336,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="166" spans="1:22">
+    <row r="166" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B166" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C166" t="s">
         <v>125</v>
@@ -14392,12 +14396,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="167" spans="1:22">
+    <row r="167" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B167" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C167" t="s">
         <v>125</v>
@@ -14452,12 +14456,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="168" spans="1:22">
+    <row r="168" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B168" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C168" t="s">
         <v>125</v>
@@ -14510,12 +14514,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="169" spans="1:22">
+    <row r="169" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B169" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C169" t="s">
         <v>125</v>
@@ -14570,12 +14574,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="170" spans="1:22">
+    <row r="170" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B170" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C170" t="s">
         <v>125</v>
@@ -14626,12 +14630,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="171" spans="1:22">
+    <row r="171" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B171" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C171" t="s">
         <v>128</v>
@@ -14686,12 +14690,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="172" spans="1:22">
+    <row r="172" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B172" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C172" t="s">
         <v>128</v>
@@ -14746,12 +14750,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="173" spans="1:22">
+    <row r="173" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B173" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C173" t="s">
         <v>125</v>
@@ -14790,12 +14794,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="174" spans="1:22">
+    <row r="174" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B174" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C174" t="s">
         <v>125</v>
@@ -14836,12 +14840,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="175" spans="1:22">
+    <row r="175" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B175" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C175" t="s">
         <v>125</v>
@@ -14896,12 +14900,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="176" spans="1:22">
+    <row r="176" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B176" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C176" t="s">
         <v>125</v>
@@ -14956,12 +14960,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="177" spans="1:22">
+    <row r="177" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B177" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C177" t="s">
         <v>125</v>
@@ -15016,12 +15020,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="178" spans="1:22">
+    <row r="178" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B178" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C178" t="s">
         <v>125</v>
@@ -15076,12 +15080,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="179" spans="1:22">
+    <row r="179" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="180" spans="1:22">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="180" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>97</v>
       </c>
@@ -15149,12 +15153,12 @@
         <v>113</v>
       </c>
     </row>
-    <row r="181" spans="1:22">
+    <row r="181" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B181" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C181" t="s">
         <v>125</v>
@@ -15196,12 +15200,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="182" spans="1:22">
+    <row r="182" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B182" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C182" t="s">
         <v>125</v>
@@ -15239,12 +15243,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="183" spans="1:22">
+    <row r="183" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B183" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C183" t="s">
         <v>116</v>
@@ -15297,12 +15301,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="184" spans="1:22">
+    <row r="184" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B184" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C184" t="s">
         <v>116</v>
@@ -15355,18 +15359,18 @@
         <v>118</v>
       </c>
     </row>
-    <row r="185" spans="1:22">
+    <row r="185" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B185" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C185" t="s">
         <v>128</v>
       </c>
       <c r="D185" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="E185" t="s">
         <v>60</v>
@@ -15413,18 +15417,18 @@
         <v>118</v>
       </c>
     </row>
-    <row r="186" spans="1:22">
+    <row r="186" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B186" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C186" t="s">
         <v>128</v>
       </c>
       <c r="D186" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="E186" t="s">
         <v>60</v>
@@ -15465,12 +15469,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="187" spans="1:22">
+    <row r="187" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B187" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C187" t="s">
         <v>128</v>
@@ -15523,12 +15527,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="188" spans="1:22">
+    <row r="188" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B188" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C188" t="s">
         <v>128</v>
@@ -15575,12 +15579,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="189" spans="1:22">
+    <row r="189" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B189" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C189" t="s">
         <v>128</v>
@@ -15628,12 +15632,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="190" spans="1:22">
+    <row r="190" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B190" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C190" t="s">
         <v>128</v>
@@ -15672,18 +15676,18 @@
         <v>118</v>
       </c>
     </row>
-    <row r="191" spans="1:22">
+    <row r="191" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B191" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C191" t="s">
         <v>128</v>
       </c>
       <c r="D191" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E191" t="s">
         <v>29</v>
@@ -15730,18 +15734,18 @@
         <v>118</v>
       </c>
     </row>
-    <row r="192" spans="1:22">
+    <row r="192" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B192" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C192" t="s">
         <v>128</v>
       </c>
       <c r="D192" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E192" t="s">
         <v>29</v>
@@ -15786,18 +15790,18 @@
         <v>118</v>
       </c>
     </row>
-    <row r="193" spans="1:22">
+    <row r="193" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B193" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C193" t="s">
         <v>128</v>
       </c>
       <c r="D193" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="E193" t="s">
         <v>29</v>
@@ -15834,18 +15838,18 @@
         <v>118</v>
       </c>
     </row>
-    <row r="194" spans="1:22">
+    <row r="194" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B194" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C194" t="s">
         <v>128</v>
       </c>
       <c r="D194" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="E194" t="s">
         <v>29</v>
@@ -15880,12 +15884,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="195" spans="1:22">
+    <row r="195" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B195" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C195" t="s">
         <v>125</v>
@@ -15928,12 +15932,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="196" spans="1:22">
+    <row r="196" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B196" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C196" t="s">
         <v>125</v>
@@ -15972,12 +15976,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="197" spans="1:22">
+    <row r="197" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B197" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C197" t="s">
         <v>125</v>
@@ -16022,12 +16026,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="198" spans="1:22">
+    <row r="198" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B198" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C198" t="s">
         <v>125</v>
@@ -16066,12 +16070,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="199" spans="1:22">
+    <row r="199" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B199" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C199" t="s">
         <v>125</v>
@@ -16124,12 +16128,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="200" spans="1:22">
+    <row r="200" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B200" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C200" t="s">
         <v>125</v>
@@ -16201,6 +16205,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -16338,38 +16357,57 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2476" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60AF97F1-CC1A-48F8-BB8E-17D1F051E183}"/>
+  <xr:revisionPtr revIDLastSave="2499" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CF0419B-AB1E-4F51-B602-3DC54ABE2290}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -847,7 +847,7 @@
     <t>Production number</t>
   </si>
   <si>
-    <t>1332/1400</t>
+    <t>1004/1365</t>
   </si>
   <si>
     <t>CTB (12 weeks)(ISC)</t>
@@ -1524,7 +1524,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1568,15 +1568,12 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -6321,28 +6318,28 @@
       <c r="H16" t="s">
         <v>118</v>
       </c>
-      <c r="I16" s="43">
+      <c r="I16">
         <v>0.93</v>
       </c>
-      <c r="J16" s="43">
+      <c r="J16">
         <v>0.8</v>
       </c>
-      <c r="K16" s="43">
+      <c r="K16">
         <v>0.92</v>
       </c>
-      <c r="L16" s="43">
+      <c r="L16">
         <v>1</v>
       </c>
-      <c r="M16" s="43">
+      <c r="M16">
         <v>0.8</v>
       </c>
-      <c r="N16" s="43">
+      <c r="N16">
         <v>0.8</v>
       </c>
-      <c r="O16" s="43">
+      <c r="O16">
         <v>0.8</v>
       </c>
-      <c r="P16" s="43">
+      <c r="P16">
         <v>0.86</v>
       </c>
       <c r="Q16" s="7"/>
@@ -6449,28 +6446,28 @@
       <c r="H18" t="s">
         <v>118</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18">
         <v>1.53</v>
       </c>
-      <c r="J18" s="43">
+      <c r="J18">
         <v>1.53</v>
       </c>
-      <c r="K18" s="43">
+      <c r="K18">
         <v>1.53</v>
       </c>
-      <c r="L18" s="43">
+      <c r="L18">
         <v>1.7</v>
       </c>
-      <c r="M18" s="43">
+      <c r="M18">
         <v>1.8</v>
       </c>
-      <c r="N18" s="43">
+      <c r="N18">
         <v>1.4</v>
       </c>
-      <c r="O18" s="43">
+      <c r="O18">
         <v>1.4</v>
       </c>
-      <c r="P18" s="43">
+      <c r="P18">
         <v>1.23</v>
       </c>
       <c r="Q18" s="7"/>
@@ -6577,28 +6574,28 @@
       <c r="H20" t="s">
         <v>118</v>
       </c>
-      <c r="I20" s="43">
+      <c r="I20">
         <v>1.7</v>
       </c>
-      <c r="J20" s="43">
+      <c r="J20">
         <v>1.76</v>
       </c>
-      <c r="K20" s="43">
+      <c r="K20">
         <v>1.78</v>
       </c>
-      <c r="L20" s="43">
+      <c r="L20">
         <v>2</v>
       </c>
-      <c r="M20" s="43">
+      <c r="M20">
         <v>2.2000000000000002</v>
       </c>
-      <c r="N20" s="43">
+      <c r="N20">
         <v>1.8</v>
       </c>
-      <c r="O20" s="43">
+      <c r="O20">
         <v>2</v>
       </c>
-      <c r="P20" s="43">
+      <c r="P20">
         <v>2.0099999999999998</v>
       </c>
       <c r="Q20" s="7"/>
@@ -7919,7 +7916,7 @@
         <v>125</v>
       </c>
       <c r="Q43">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="R43">
         <v>112</v>
@@ -7928,7 +7925,7 @@
         <v>110</v>
       </c>
       <c r="T43">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="U43" t="s">
         <v>32</v>
@@ -8152,7 +8149,7 @@
         <v>116</v>
       </c>
       <c r="I47" s="4">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J47" s="4">
         <v>0.9</v>
@@ -8161,7 +8158,7 @@
         <v>0.95</v>
       </c>
       <c r="L47" s="4">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="M47" s="4">
         <v>0.9</v>
@@ -8170,14 +8167,12 @@
         <v>0.95</v>
       </c>
       <c r="O47" s="4">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="P47" s="4">
         <v>0.95</v>
       </c>
-      <c r="Q47" s="4">
-        <v>1</v>
-      </c>
+      <c r="Q47" s="4"/>
       <c r="R47" s="4" t="s">
         <v>164</v>
       </c>
@@ -8243,9 +8238,7 @@
       <c r="P48" s="4">
         <v>0.71</v>
       </c>
-      <c r="Q48" s="4">
-        <v>0.83799999999999997</v>
-      </c>
+      <c r="Q48" s="4"/>
       <c r="R48" s="4" t="s">
         <v>164</v>
       </c>
@@ -8355,28 +8348,28 @@
       <c r="H50" t="s">
         <v>118</v>
       </c>
-      <c r="I50" s="43">
+      <c r="I50">
         <v>17.3</v>
       </c>
-      <c r="J50" s="43">
+      <c r="J50">
         <v>21.89</v>
       </c>
-      <c r="K50" s="43">
+      <c r="K50">
         <v>21.44</v>
       </c>
-      <c r="L50" s="43">
+      <c r="L50">
         <v>24.02</v>
       </c>
-      <c r="M50" s="43">
+      <c r="M50">
         <v>24.1</v>
       </c>
-      <c r="N50" s="43">
+      <c r="N50">
         <v>22.5</v>
       </c>
-      <c r="O50" s="43">
+      <c r="O50">
         <v>23</v>
       </c>
-      <c r="P50" s="43">
+      <c r="P50">
         <v>25.31</v>
       </c>
       <c r="Q50" s="8"/>
@@ -8415,40 +8408,40 @@
       <c r="H51" t="s">
         <v>116</v>
       </c>
-      <c r="I51" s="43">
+      <c r="I51">
         <v>15</v>
       </c>
-      <c r="J51" s="43">
+      <c r="J51">
         <v>15</v>
       </c>
-      <c r="K51" s="43">
+      <c r="K51">
         <v>15</v>
       </c>
-      <c r="L51" s="43">
+      <c r="L51">
         <v>15</v>
       </c>
-      <c r="M51" s="43">
+      <c r="M51">
         <v>15</v>
       </c>
-      <c r="N51" s="43">
+      <c r="N51">
         <v>15</v>
       </c>
-      <c r="O51" s="43">
+      <c r="O51">
         <v>15</v>
       </c>
-      <c r="P51" s="43">
+      <c r="P51">
         <v>15</v>
       </c>
-      <c r="Q51" s="43">
+      <c r="Q51">
         <v>15</v>
       </c>
-      <c r="R51" s="43">
+      <c r="R51">
         <v>15</v>
       </c>
-      <c r="S51" s="43">
+      <c r="S51">
         <v>15</v>
       </c>
-      <c r="T51" s="43">
+      <c r="T51">
         <v>15</v>
       </c>
       <c r="U51" t="s">
@@ -8483,32 +8476,32 @@
       <c r="H52" t="s">
         <v>118</v>
       </c>
-      <c r="I52" s="43">
+      <c r="I52">
         <v>7</v>
       </c>
-      <c r="J52" s="43">
+      <c r="J52">
         <v>8</v>
       </c>
-      <c r="K52" s="43">
+      <c r="K52">
         <v>28</v>
       </c>
-      <c r="L52" s="43">
+      <c r="L52">
         <v>16</v>
       </c>
-      <c r="M52" s="43">
+      <c r="M52">
         <v>20</v>
       </c>
-      <c r="N52" s="43">
+      <c r="N52">
         <v>9</v>
       </c>
-      <c r="O52" s="43">
+      <c r="O52">
         <v>13</v>
       </c>
-      <c r="P52" s="43">
+      <c r="P52">
         <v>5</v>
       </c>
-      <c r="Q52" s="43">
-        <v>19</v>
+      <c r="Q52">
+        <v>15</v>
       </c>
       <c r="R52" s="8"/>
       <c r="S52" s="8"/>
@@ -8613,31 +8606,31 @@
       <c r="H54" t="s">
         <v>118</v>
       </c>
-      <c r="I54" s="43">
+      <c r="I54">
         <v>4.0999999999999996</v>
       </c>
-      <c r="J54" s="43">
+      <c r="J54">
         <v>9.8000000000000007</v>
       </c>
-      <c r="K54" s="43">
+      <c r="K54">
         <v>25.3</v>
       </c>
-      <c r="L54" s="43">
+      <c r="L54">
         <v>31.44</v>
       </c>
-      <c r="M54" s="43">
+      <c r="M54">
         <v>40.9</v>
       </c>
-      <c r="N54" s="43">
+      <c r="N54">
         <v>55.18</v>
       </c>
-      <c r="O54" s="43">
+      <c r="O54">
         <v>61.4</v>
       </c>
-      <c r="P54" s="43">
+      <c r="P54">
         <v>72.7</v>
       </c>
-      <c r="Q54" s="43">
+      <c r="Q54">
         <v>88.2</v>
       </c>
       <c r="R54" s="8"/>
@@ -9503,10 +9496,10 @@
       <c r="J68" s="7">
         <v>0.04</v>
       </c>
-      <c r="K68" s="44">
+      <c r="K68" s="43">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="L68" s="44">
+      <c r="L68" s="43">
         <v>0</v>
       </c>
       <c r="M68" s="18">
@@ -10055,19 +10048,19 @@
       <c r="H77" t="s">
         <v>116</v>
       </c>
-      <c r="I77" s="43">
+      <c r="I77">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="J77" s="43">
+      <c r="J77">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="K77" s="43">
+      <c r="K77">
         <v>0.10500000000000001</v>
       </c>
-      <c r="L77" s="43">
+      <c r="L77">
         <v>0.14000000000000001</v>
       </c>
-      <c r="M77" s="43">
+      <c r="M77">
         <v>0.17500000000000002</v>
       </c>
       <c r="N77">
@@ -10135,7 +10128,7 @@
       <c r="L78" s="18">
         <v>0.152422</v>
       </c>
-      <c r="M78" s="43">
+      <c r="M78">
         <v>0.19</v>
       </c>
       <c r="N78">
@@ -10482,7 +10475,7 @@
       <c r="A85" t="s">
         <v>204</v>
       </c>
-      <c r="B85" s="45" t="s">
+      <c r="B85" s="44" t="s">
         <v>205</v>
       </c>
       <c r="C85" t="s">
@@ -10550,7 +10543,7 @@
       <c r="A86" t="s">
         <v>204</v>
       </c>
-      <c r="B86" s="45" t="s">
+      <c r="B86" s="44" t="s">
         <v>205</v>
       </c>
       <c r="C86" t="s">
@@ -11069,40 +11062,40 @@
       <c r="H95" t="s">
         <v>116</v>
       </c>
-      <c r="I95" s="43">
+      <c r="I95">
         <v>80</v>
       </c>
-      <c r="J95" s="43">
+      <c r="J95">
         <v>80</v>
       </c>
-      <c r="K95" s="43">
+      <c r="K95">
         <v>80</v>
       </c>
-      <c r="L95" s="43">
+      <c r="L95">
         <v>80</v>
       </c>
-      <c r="M95" s="43">
+      <c r="M95">
         <v>80</v>
       </c>
-      <c r="N95" s="43">
+      <c r="N95">
         <v>80</v>
       </c>
-      <c r="O95" s="43">
+      <c r="O95">
         <v>80</v>
       </c>
-      <c r="P95" s="43">
+      <c r="P95">
         <v>80</v>
       </c>
-      <c r="Q95" s="43">
+      <c r="Q95">
         <v>80</v>
       </c>
-      <c r="R95" s="43">
+      <c r="R95">
         <v>80</v>
       </c>
-      <c r="S95" s="43">
+      <c r="S95">
         <v>80</v>
       </c>
-      <c r="T95" s="43">
+      <c r="T95">
         <v>80</v>
       </c>
       <c r="U95" t="s">
@@ -11137,25 +11130,25 @@
       <c r="H96" t="s">
         <v>118</v>
       </c>
-      <c r="I96" s="43">
+      <c r="I96">
         <v>86</v>
       </c>
-      <c r="J96" s="43">
+      <c r="J96">
         <v>88</v>
       </c>
-      <c r="K96" s="43">
+      <c r="K96">
         <v>100</v>
       </c>
-      <c r="L96" s="43">
+      <c r="L96">
         <v>100</v>
       </c>
-      <c r="M96" s="43">
+      <c r="M96">
         <v>87.5</v>
       </c>
-      <c r="N96" s="43">
+      <c r="N96">
         <v>100</v>
       </c>
-      <c r="O96" s="43">
+      <c r="O96">
         <v>100</v>
       </c>
       <c r="P96" s="8"/>
@@ -11729,8 +11722,12 @@
       <c r="O106" s="17">
         <v>77</v>
       </c>
-      <c r="P106" s="17"/>
-      <c r="Q106" s="17"/>
+      <c r="P106" s="17">
+        <v>77</v>
+      </c>
+      <c r="Q106" s="17">
+        <v>75</v>
+      </c>
       <c r="R106" s="17"/>
       <c r="S106" s="17"/>
       <c r="T106" s="17"/>
@@ -11855,6 +11852,12 @@
       <c r="O108">
         <v>84</v>
       </c>
+      <c r="P108">
+        <v>77</v>
+      </c>
+      <c r="Q108">
+        <v>87</v>
+      </c>
       <c r="U108" t="s">
         <v>40</v>
       </c>
@@ -11976,6 +11979,9 @@
       <c r="O110">
         <v>89</v>
       </c>
+      <c r="P110">
+        <v>88</v>
+      </c>
       <c r="U110" t="s">
         <v>40</v>
       </c>
@@ -12097,8 +12103,12 @@
       <c r="O112" s="2">
         <v>0.35599999999999998</v>
       </c>
-      <c r="P112" s="2"/>
-      <c r="Q112" s="2"/>
+      <c r="P112" s="2">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="Q112" s="3">
+        <v>0.35199999999999998</v>
+      </c>
       <c r="R112" s="2"/>
       <c r="S112" s="2"/>
       <c r="T112" s="2"/>
@@ -12219,8 +12229,12 @@
       <c r="O114" s="2">
         <v>0.19</v>
       </c>
-      <c r="P114" s="3"/>
-      <c r="Q114" s="3"/>
+      <c r="P114" s="2">
+        <v>0.24</v>
+      </c>
+      <c r="Q114" s="2">
+        <v>0.28000000000000003</v>
+      </c>
       <c r="R114" s="3"/>
       <c r="S114" s="3"/>
       <c r="T114" s="3"/>
@@ -12337,7 +12351,9 @@
       <c r="O116" s="2">
         <v>0.81</v>
       </c>
-      <c r="P116" s="2"/>
+      <c r="P116" s="2">
+        <v>0.82</v>
+      </c>
       <c r="Q116" s="2"/>
       <c r="R116" s="2"/>
       <c r="S116" s="2"/>
@@ -12575,40 +12591,40 @@
       <c r="H121" t="s">
         <v>116</v>
       </c>
-      <c r="I121" s="49">
+      <c r="I121" s="4">
         <v>0.4</v>
       </c>
-      <c r="J121" s="49">
+      <c r="J121" s="4">
         <v>0.4</v>
       </c>
-      <c r="K121" s="49">
+      <c r="K121" s="4">
         <v>0.4</v>
       </c>
-      <c r="L121" s="49">
+      <c r="L121" s="4">
         <v>0.4</v>
       </c>
-      <c r="M121" s="49">
+      <c r="M121" s="4">
         <v>0.4</v>
       </c>
-      <c r="N121" s="49">
+      <c r="N121" s="4">
         <v>0.4</v>
       </c>
-      <c r="O121" s="49">
+      <c r="O121" s="4">
         <v>0.4</v>
       </c>
-      <c r="P121" s="49">
+      <c r="P121" s="4">
         <v>0.4</v>
       </c>
-      <c r="Q121" s="49">
+      <c r="Q121" s="4">
         <v>0.4</v>
       </c>
-      <c r="R121" s="49">
+      <c r="R121" s="4">
         <v>0.4</v>
       </c>
-      <c r="S121" s="49">
+      <c r="S121" s="4">
         <v>0.4</v>
       </c>
-      <c r="T121" s="49">
+      <c r="T121" s="4">
         <v>0.4</v>
       </c>
       <c r="U121" t="s">
@@ -12658,7 +12674,7 @@
       <c r="M122" s="4">
         <v>0.32</v>
       </c>
-      <c r="N122" s="49">
+      <c r="N122" s="4">
         <v>0.42</v>
       </c>
       <c r="O122" s="6">
@@ -12936,7 +12952,7 @@
       <c r="C127" t="s">
         <v>127</v>
       </c>
-      <c r="D127" s="48">
+      <c r="D127" s="46">
         <v>0.23599999999999999</v>
       </c>
       <c r="E127" t="s">
@@ -12969,7 +12985,7 @@
       <c r="N127" s="12">
         <v>0.22774534528665999</v>
       </c>
-      <c r="O127" s="46">
+      <c r="O127" s="12">
         <v>0.22918662334807141</v>
       </c>
       <c r="P127" s="15">
@@ -13004,7 +13020,7 @@
       <c r="C128" t="s">
         <v>127</v>
       </c>
-      <c r="D128" s="48">
+      <c r="D128" s="46">
         <v>0.23599999999999999</v>
       </c>
       <c r="E128" t="s">
@@ -13040,7 +13056,7 @@
       <c r="O128" s="15">
         <v>0.24</v>
       </c>
-      <c r="P128" s="46">
+      <c r="P128" s="12">
         <v>0.24</v>
       </c>
       <c r="Q128" s="15"/>
@@ -13064,7 +13080,7 @@
       <c r="C129" t="s">
         <v>127</v>
       </c>
-      <c r="D129" s="48">
+      <c r="D129" s="46">
         <v>0.81599999999999995</v>
       </c>
       <c r="E129" t="s">
@@ -13097,7 +13113,7 @@
       <c r="N129" s="12">
         <v>0.80900000000000005</v>
       </c>
-      <c r="O129" s="46">
+      <c r="O129" s="12">
         <v>0.81</v>
       </c>
       <c r="P129" s="15">
@@ -13132,7 +13148,7 @@
       <c r="C130" t="s">
         <v>127</v>
       </c>
-      <c r="D130" s="48">
+      <c r="D130" s="46">
         <v>0.81599999999999995</v>
       </c>
       <c r="E130" t="s">
@@ -13225,22 +13241,22 @@
       <c r="N131" s="12">
         <v>0.7</v>
       </c>
-      <c r="O131" s="46">
+      <c r="O131" s="12">
         <v>0.7</v>
       </c>
-      <c r="P131" s="46">
+      <c r="P131" s="12">
         <v>0.7</v>
       </c>
-      <c r="Q131" s="46">
+      <c r="Q131" s="12">
         <v>0.7</v>
       </c>
-      <c r="R131" s="46">
+      <c r="R131" s="12">
         <v>0.7</v>
       </c>
-      <c r="S131" s="46">
+      <c r="S131" s="12">
         <v>0.7</v>
       </c>
-      <c r="T131" s="46">
+      <c r="T131" s="12">
         <v>0.7</v>
       </c>
       <c r="U131" t="s">
@@ -13296,7 +13312,7 @@
       <c r="O132" s="15">
         <v>0.69699999999999995</v>
       </c>
-      <c r="P132" s="46">
+      <c r="P132" s="12">
         <v>0.7</v>
       </c>
       <c r="Q132" s="15"/>
@@ -13394,7 +13410,7 @@
       </c>
       <c r="L134" s="15"/>
       <c r="M134" s="15"/>
-      <c r="N134" s="46">
+      <c r="N134" s="12">
         <v>0.91</v>
       </c>
       <c r="O134" s="15"/>
@@ -13506,7 +13522,7 @@
       <c r="K136" s="20">
         <v>17.7</v>
       </c>
-      <c r="L136" s="47">
+      <c r="L136" s="45">
         <v>23.77</v>
       </c>
       <c r="M136" s="20">
@@ -13542,7 +13558,7 @@
       <c r="C137" t="s">
         <v>127</v>
       </c>
-      <c r="D137" s="48">
+      <c r="D137" s="46">
         <v>0.52700000000000002</v>
       </c>
       <c r="E137" t="s">
@@ -13610,7 +13626,7 @@
       <c r="C138" t="s">
         <v>127</v>
       </c>
-      <c r="D138" s="48">
+      <c r="D138" s="46">
         <v>0.52700000000000002</v>
       </c>
       <c r="E138" t="s">
@@ -13637,10 +13653,10 @@
       <c r="L138" s="13">
         <v>0.42799999999999999</v>
       </c>
-      <c r="M138" s="46">
+      <c r="M138" s="12">
         <v>0.43</v>
       </c>
-      <c r="N138" s="46">
+      <c r="N138" s="12">
         <v>0.45</v>
       </c>
       <c r="O138" s="15">
@@ -13882,22 +13898,22 @@
       <c r="H143" t="s">
         <v>116</v>
       </c>
-      <c r="I143" s="43">
+      <c r="I143">
         <v>7</v>
       </c>
-      <c r="J143" s="43">
+      <c r="J143">
         <v>8</v>
       </c>
-      <c r="K143" s="43">
+      <c r="K143">
         <v>10</v>
       </c>
-      <c r="L143" s="43">
+      <c r="L143">
         <v>9</v>
       </c>
-      <c r="M143" s="43">
+      <c r="M143">
         <v>10</v>
       </c>
-      <c r="N143" s="43">
+      <c r="N143">
         <v>12</v>
       </c>
       <c r="O143">
@@ -13950,22 +13966,22 @@
       <c r="H144" t="s">
         <v>118</v>
       </c>
-      <c r="I144" s="43">
+      <c r="I144">
         <v>10</v>
       </c>
-      <c r="J144" s="43">
+      <c r="J144">
         <v>9</v>
       </c>
-      <c r="K144" s="43">
+      <c r="K144">
         <v>6</v>
       </c>
-      <c r="L144" s="43">
+      <c r="L144">
         <v>7.5</v>
       </c>
-      <c r="M144" s="43">
+      <c r="M144">
         <v>8</v>
       </c>
-      <c r="N144" s="43">
+      <c r="N144">
         <v>11</v>
       </c>
       <c r="O144">
@@ -14003,40 +14019,40 @@
       <c r="H145" t="s">
         <v>116</v>
       </c>
-      <c r="I145" s="43">
+      <c r="I145">
         <v>50</v>
       </c>
-      <c r="J145" s="43">
+      <c r="J145">
         <v>50</v>
       </c>
-      <c r="K145" s="43">
+      <c r="K145">
         <v>50</v>
       </c>
-      <c r="L145" s="43">
+      <c r="L145">
         <v>50</v>
       </c>
-      <c r="M145" s="43">
+      <c r="M145">
         <v>50</v>
       </c>
-      <c r="N145" s="43">
+      <c r="N145">
         <v>50</v>
       </c>
-      <c r="O145" s="43">
+      <c r="O145">
         <v>50</v>
       </c>
-      <c r="P145" s="43">
+      <c r="P145">
         <v>50</v>
       </c>
-      <c r="Q145" s="43">
+      <c r="Q145">
         <v>50</v>
       </c>
-      <c r="R145" s="43">
+      <c r="R145">
         <v>50</v>
       </c>
-      <c r="S145" s="43">
+      <c r="S145">
         <v>50</v>
       </c>
-      <c r="T145" s="43">
+      <c r="T145">
         <v>50</v>
       </c>
       <c r="U145" t="s">
@@ -14083,13 +14099,13 @@
       <c r="L146" s="17">
         <v>38.5</v>
       </c>
-      <c r="M146" s="43">
+      <c r="M146">
         <v>85.7</v>
       </c>
-      <c r="N146" s="43">
+      <c r="N146">
         <v>42.9</v>
       </c>
-      <c r="O146" s="43">
+      <c r="O146">
         <v>100</v>
       </c>
       <c r="P146" s="8"/>
@@ -14129,40 +14145,40 @@
       <c r="H147" t="s">
         <v>116</v>
       </c>
-      <c r="I147" s="43">
+      <c r="I147">
         <v>26</v>
       </c>
-      <c r="J147" s="43">
+      <c r="J147">
         <v>26</v>
       </c>
-      <c r="K147" s="43">
+      <c r="K147">
         <v>26</v>
       </c>
-      <c r="L147" s="43">
+      <c r="L147">
         <v>26</v>
       </c>
-      <c r="M147" s="43">
+      <c r="M147">
         <v>26</v>
       </c>
-      <c r="N147" s="43">
+      <c r="N147">
         <v>26</v>
       </c>
-      <c r="O147" s="43">
+      <c r="O147">
         <v>26</v>
       </c>
-      <c r="P147" s="43">
+      <c r="P147">
         <v>26</v>
       </c>
-      <c r="Q147" s="43">
+      <c r="Q147">
         <v>26</v>
       </c>
-      <c r="R147" s="43">
+      <c r="R147">
         <v>26</v>
       </c>
-      <c r="S147" s="43">
+      <c r="S147">
         <v>26</v>
       </c>
-      <c r="T147" s="43">
+      <c r="T147">
         <v>26</v>
       </c>
       <c r="U147" t="s">
@@ -14197,13 +14213,13 @@
       <c r="H148" t="s">
         <v>118</v>
       </c>
-      <c r="I148" s="43">
+      <c r="I148">
         <v>17.8</v>
       </c>
-      <c r="J148" s="43">
+      <c r="J148">
         <v>17.8</v>
       </c>
-      <c r="K148" s="43">
+      <c r="K148">
         <v>17.8</v>
       </c>
       <c r="L148" s="8"/>
@@ -14247,40 +14263,40 @@
       <c r="H149" t="s">
         <v>116</v>
       </c>
-      <c r="I149" s="43">
+      <c r="I149">
         <v>28</v>
       </c>
-      <c r="J149" s="43">
+      <c r="J149">
         <v>28</v>
       </c>
-      <c r="K149" s="43">
+      <c r="K149">
         <v>28</v>
       </c>
-      <c r="L149" s="43">
+      <c r="L149">
         <v>28</v>
       </c>
-      <c r="M149" s="43">
+      <c r="M149">
         <v>28</v>
       </c>
-      <c r="N149" s="43">
+      <c r="N149">
         <v>28</v>
       </c>
-      <c r="O149" s="43">
+      <c r="O149">
         <v>28</v>
       </c>
-      <c r="P149" s="43">
+      <c r="P149">
         <v>28</v>
       </c>
-      <c r="Q149" s="43">
+      <c r="Q149">
         <v>28</v>
       </c>
-      <c r="R149" s="43">
+      <c r="R149">
         <v>28</v>
       </c>
-      <c r="S149" s="43">
+      <c r="S149">
         <v>28</v>
       </c>
-      <c r="T149" s="43">
+      <c r="T149">
         <v>28</v>
       </c>
       <c r="U149" t="s">
@@ -14315,25 +14331,25 @@
       <c r="H150" t="s">
         <v>118</v>
       </c>
-      <c r="I150" s="43">
+      <c r="I150">
         <v>26</v>
       </c>
-      <c r="J150" s="43">
+      <c r="J150">
         <v>45.7</v>
       </c>
-      <c r="K150" s="43">
+      <c r="K150">
         <v>44</v>
       </c>
-      <c r="L150" s="43">
+      <c r="L150">
         <v>31.5</v>
       </c>
-      <c r="M150" s="43">
+      <c r="M150">
         <v>26.5</v>
       </c>
-      <c r="N150" s="43">
+      <c r="N150">
         <v>52</v>
       </c>
-      <c r="O150" s="43">
+      <c r="O150">
         <v>38</v>
       </c>
       <c r="P150" s="8"/>
@@ -14517,22 +14533,22 @@
       <c r="N153" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="O153" s="49">
+      <c r="O153" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="P153" s="49">
+      <c r="P153" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="Q153" s="49">
+      <c r="Q153" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="R153" s="49">
+      <c r="R153" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="S153" s="49">
+      <c r="S153" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="T153" s="49">
+      <c r="T153" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="U153" t="s">
@@ -14743,40 +14759,40 @@
       <c r="H157" t="s">
         <v>116</v>
       </c>
-      <c r="I157" s="50">
+      <c r="I157" s="47">
         <v>40</v>
       </c>
-      <c r="J157" s="50">
+      <c r="J157" s="47">
         <v>40</v>
       </c>
-      <c r="K157" s="50">
+      <c r="K157" s="47">
         <v>40</v>
       </c>
-      <c r="L157" s="50">
+      <c r="L157" s="47">
         <v>40</v>
       </c>
-      <c r="M157" s="50">
+      <c r="M157" s="47">
         <v>40</v>
       </c>
-      <c r="N157" s="50">
+      <c r="N157" s="47">
         <v>40</v>
       </c>
-      <c r="O157" s="50">
+      <c r="O157" s="47">
         <v>40</v>
       </c>
-      <c r="P157" s="50">
+      <c r="P157" s="47">
         <v>40</v>
       </c>
-      <c r="Q157" s="50">
+      <c r="Q157" s="47">
         <v>40</v>
       </c>
-      <c r="R157" s="50">
+      <c r="R157" s="47">
         <v>40</v>
       </c>
-      <c r="S157" s="50">
+      <c r="S157" s="47">
         <v>40</v>
       </c>
-      <c r="T157" s="50">
+      <c r="T157" s="47">
         <v>40</v>
       </c>
       <c r="U157" t="s">
@@ -15064,40 +15080,40 @@
       <c r="H163" t="s">
         <v>116</v>
       </c>
-      <c r="I163" s="46">
+      <c r="I163" s="12">
         <v>0.6</v>
       </c>
-      <c r="J163" s="46">
+      <c r="J163" s="12">
         <v>0.8</v>
       </c>
-      <c r="K163" s="46">
+      <c r="K163" s="12">
         <v>1</v>
       </c>
-      <c r="L163" s="46">
+      <c r="L163" s="12">
         <v>0.6</v>
       </c>
-      <c r="M163" s="46">
+      <c r="M163" s="12">
         <v>0.8</v>
       </c>
-      <c r="N163" s="46">
+      <c r="N163" s="12">
         <v>1</v>
       </c>
-      <c r="O163" s="46">
+      <c r="O163" s="12">
         <v>0.6</v>
       </c>
-      <c r="P163" s="46">
+      <c r="P163" s="12">
         <v>0.8</v>
       </c>
-      <c r="Q163" s="46">
+      <c r="Q163" s="12">
         <v>1</v>
       </c>
-      <c r="R163" s="46">
+      <c r="R163" s="12">
         <v>0.6</v>
       </c>
-      <c r="S163" s="46">
+      <c r="S163" s="12">
         <v>0.8</v>
       </c>
-      <c r="T163" s="46">
+      <c r="T163" s="12">
         <v>1</v>
       </c>
       <c r="U163" t="s">
@@ -15132,31 +15148,31 @@
       <c r="H164" t="s">
         <v>118</v>
       </c>
-      <c r="I164" s="46">
+      <c r="I164" s="12">
         <v>0.6</v>
       </c>
-      <c r="J164" s="46">
+      <c r="J164" s="12">
         <v>0.81</v>
       </c>
-      <c r="K164" s="46">
+      <c r="K164" s="12">
         <v>1.05</v>
       </c>
-      <c r="L164" s="46">
+      <c r="L164" s="12">
         <v>0.37</v>
       </c>
-      <c r="M164" s="46">
+      <c r="M164" s="12">
         <v>0.42</v>
       </c>
-      <c r="N164" s="46">
+      <c r="N164" s="12">
         <v>0.7</v>
       </c>
-      <c r="O164" s="46">
+      <c r="O164" s="12">
         <v>0.6</v>
       </c>
-      <c r="P164" s="46">
+      <c r="P164" s="12">
         <v>0.63</v>
       </c>
-      <c r="Q164" s="46">
+      <c r="Q164" s="12">
         <v>0.67</v>
       </c>
       <c r="R164" s="36"/>
@@ -15433,7 +15449,7 @@
       <c r="C169" t="s">
         <v>127</v>
       </c>
-      <c r="D169" s="48">
+      <c r="D169" s="46">
         <v>0.41299999999999998</v>
       </c>
       <c r="E169" t="s">
@@ -15501,7 +15517,7 @@
       <c r="C170" t="s">
         <v>127</v>
       </c>
-      <c r="D170" s="48">
+      <c r="D170" s="46">
         <v>0.41299999999999998</v>
       </c>
       <c r="E170" t="s">
@@ -15561,7 +15577,7 @@
       <c r="C171" t="s">
         <v>124</v>
       </c>
-      <c r="D171" s="48">
+      <c r="D171" s="46">
         <v>0.16500000000000001</v>
       </c>
       <c r="E171" t="s">
@@ -15607,7 +15623,7 @@
       <c r="C172" t="s">
         <v>124</v>
       </c>
-      <c r="D172" s="48">
+      <c r="D172" s="46">
         <v>0.16500000000000001</v>
       </c>
       <c r="E172" t="s">
@@ -15911,7 +15927,7 @@
       <c r="C177" t="s">
         <v>127</v>
       </c>
-      <c r="D177" s="43">
+      <c r="D177">
         <v>126</v>
       </c>
       <c r="E177" t="s">
@@ -15979,7 +15995,7 @@
       <c r="C178" t="s">
         <v>127</v>
       </c>
-      <c r="D178" s="43">
+      <c r="D178">
         <v>126</v>
       </c>
       <c r="E178" t="s">
@@ -16021,9 +16037,9 @@
       <c r="Q178" s="20">
         <v>9.1999999999999993</v>
       </c>
-      <c r="R178" s="47"/>
-      <c r="S178" s="47"/>
-      <c r="T178" s="47"/>
+      <c r="R178" s="45"/>
+      <c r="S178" s="45"/>
+      <c r="T178" s="45"/>
       <c r="U178" t="s">
         <v>40</v>
       </c>
@@ -16417,16 +16433,16 @@
       <c r="H186" t="s">
         <v>118</v>
       </c>
-      <c r="I186" s="43">
+      <c r="I186">
         <v>6.4</v>
       </c>
-      <c r="J186" s="43">
+      <c r="J186">
         <v>8.6</v>
       </c>
-      <c r="K186" s="43">
+      <c r="K186">
         <v>17</v>
       </c>
-      <c r="L186" s="43">
+      <c r="L186">
         <v>13</v>
       </c>
       <c r="M186" s="8"/>
@@ -17201,25 +17217,25 @@
       <c r="H200" t="s">
         <v>118</v>
       </c>
-      <c r="I200" s="43">
+      <c r="I200">
         <v>2</v>
       </c>
-      <c r="J200" s="43">
+      <c r="J200">
         <v>2.2000000000000002</v>
       </c>
-      <c r="K200" s="43">
+      <c r="K200">
         <v>2.5</v>
       </c>
-      <c r="L200" s="43">
+      <c r="L200">
         <v>2.4</v>
       </c>
-      <c r="M200" s="43">
+      <c r="M200">
         <v>3.1</v>
       </c>
-      <c r="N200" s="43">
+      <c r="N200">
         <v>3.8</v>
       </c>
-      <c r="O200" s="43">
+      <c r="O200">
         <v>2.2000000000000002</v>
       </c>
       <c r="P200" s="8"/>
@@ -17255,12 +17271,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -17398,32 +17422,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
 </file>
--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2501" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3195DCB8-8A8B-4A52-B15F-19F6E5DE4544}"/>
+  <xr:revisionPtr revIDLastSave="2504" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D13AC2E-56B2-44C1-AD2A-F57D13AD7F48}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1524,7 +1524,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1575,6 +1575,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13367,7 +13368,9 @@
         <v>0.79</v>
       </c>
       <c r="R133" s="15"/>
-      <c r="S133" s="15"/>
+      <c r="S133" s="15">
+        <v>0.8</v>
+      </c>
       <c r="T133" s="15">
         <v>0.79</v>
       </c>
@@ -13419,7 +13422,9 @@
         <v>0.91</v>
       </c>
       <c r="R134" s="15"/>
-      <c r="S134" s="15"/>
+      <c r="S134" s="48">
+        <v>0.8</v>
+      </c>
       <c r="T134" s="15"/>
       <c r="U134" t="s">
         <v>32</v>
@@ -17272,20 +17277,10 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -17423,23 +17418,33 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
 </file>
--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2504" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D13AC2E-56B2-44C1-AD2A-F57D13AD7F48}"/>
+  <xr:revisionPtr revIDLastSave="2506" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{501DA872-2CE7-4C3B-98ED-EB848999A8AB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1524,7 +1524,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1575,7 +1575,6 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13368,9 +13367,7 @@
         <v>0.79</v>
       </c>
       <c r="R133" s="15"/>
-      <c r="S133" s="15">
-        <v>0.8</v>
-      </c>
+      <c r="S133" s="15"/>
       <c r="T133" s="15">
         <v>0.79</v>
       </c>
@@ -13422,9 +13419,7 @@
         <v>0.91</v>
       </c>
       <c r="R134" s="15"/>
-      <c r="S134" s="48">
-        <v>0.8</v>
-      </c>
+      <c r="S134" s="12"/>
       <c r="T134" s="15"/>
       <c r="U134" t="s">
         <v>32</v>
@@ -17276,8 +17271,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17419,9 +17415,8 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17434,7 +17429,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17442,7 +17437,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -1486,10 +1486,14 @@
       <c r="R6" s="49" t="n">
         <v>0.035</v>
       </c>
-      <c r="S6" s="49" t="n"/>
+      <c r="S6" s="49" t="n">
+        <v>0.035</v>
+      </c>
       <c r="T6" s="49" t="n"/>
       <c r="U6" s="49" t="n"/>
-      <c r="V6" s="49" t="n"/>
+      <c r="V6" s="49" t="n">
+        <v>0.06</v>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>Percentage</t>
@@ -1630,7 +1634,9 @@
       <c r="R8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="S8" s="13" t="n"/>
+      <c r="S8" s="13" t="n">
+        <v>1</v>
+      </c>
       <c r="T8" s="13" t="n"/>
       <c r="U8" s="13" t="n"/>
       <c r="V8" s="13" t="n"/>
@@ -1770,6 +1776,9 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="inlineStr">

--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2521" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3DB2402-DF70-4C22-8000-C8417FB87F0C}"/>
+  <xr:revisionPtr revIDLastSave="2523" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CBC2ACA-B050-45C8-B7E8-C3C369299AAA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3797,8 +3797,8 @@
       <c r="R26" s="7">
         <v>3.895</v>
       </c>
-      <c r="S26">
-        <v>4.92</v>
+      <c r="S26" s="7">
+        <v>5.0119999999999996</v>
       </c>
       <c r="T26" s="7"/>
       <c r="U26" s="7"/>
@@ -17297,11 +17297,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -17439,13 +17434,12 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -17454,18 +17448,24 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
 </file>
--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2523" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CBC2ACA-B050-45C8-B7E8-C3C369299AAA}"/>
+  <xr:revisionPtr revIDLastSave="2524" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A978760-398E-4AB2-A9B4-CAB94B51ADF6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3039,7 +3039,9 @@
       <c r="R12" s="6">
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="S12" s="6"/>
+      <c r="S12" s="6">
+        <v>1.7000000000000001E-2</v>
+      </c>
       <c r="T12" s="6"/>
       <c r="U12" s="6"/>
       <c r="V12" s="6"/>
@@ -17297,6 +17299,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -17434,20 +17450,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -17455,7 +17457,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17463,7 +17465,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/Masterfile_DMB_Dashboard.xlsx
+++ b/data/Masterfile_DMB_Dashboard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://share.philips.com/sites/MoSDMBData_Sharing/Shared Documents/MoS DMB Dashboard- Data Sharing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2528" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94850FAE-8286-4D87-8CE2-DBBB60F6A640}"/>
+  <xr:revisionPtr revIDLastSave="2534" documentId="120_S{A17216AA-736B-55D6-B1BA-EA961D9A6960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05AC9672-95C1-417C-BF09-27EF830F2E30}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4468,8 +4468,12 @@
       <c r="Q38" s="4">
         <v>0.56000000000000005</v>
       </c>
-      <c r="R38" s="4"/>
-      <c r="S38" s="4"/>
+      <c r="R38" s="4">
+        <v>0.39</v>
+      </c>
+      <c r="S38" s="4">
+        <v>0.37</v>
+      </c>
       <c r="T38" s="4"/>
       <c r="U38" s="4"/>
       <c r="V38" s="4"/>
@@ -4834,7 +4838,9 @@
       <c r="R45" s="4">
         <v>0.34</v>
       </c>
-      <c r="S45" s="4"/>
+      <c r="S45" s="4">
+        <v>0.34</v>
+      </c>
       <c r="T45" s="4"/>
       <c r="U45" s="4"/>
       <c r="V45" s="4"/>
@@ -4891,7 +4897,9 @@
       <c r="R46" s="4">
         <v>0.35</v>
       </c>
-      <c r="S46" s="4"/>
+      <c r="S46" s="4">
+        <v>0.35</v>
+      </c>
       <c r="T46" s="4"/>
       <c r="U46" s="4"/>
       <c r="V46" s="4"/>
@@ -12019,6 +12027,9 @@
       <c r="P110">
         <v>88</v>
       </c>
+      <c r="Q110">
+        <v>91</v>
+      </c>
       <c r="U110" t="s">
         <v>40</v>
       </c>
@@ -12391,7 +12402,9 @@
       <c r="P116" s="2">
         <v>0.82</v>
       </c>
-      <c r="Q116" s="2"/>
+      <c r="Q116" s="2">
+        <v>0.81</v>
+      </c>
       <c r="R116" s="2"/>
       <c r="S116" s="2"/>
       <c r="T116" s="2"/>
@@ -17309,10 +17322,20 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2562963771C61468D5985509A74B113" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8b7c9263bd04fb6e5f560e46093df446">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc9d53a9c0f348cc35d5ded16450d42c" ns2:_="">
     <xsd:import namespace="11ebe5d0-3002-4d7d-ad07-cedfcddd21c5"/>
@@ -17450,33 +17473,23 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e40374fb-a6cc-4854-989f-c1d94a7967ee" ContentTypeId="0x01" PreviousValue="false"/>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C3A709-78B8-4832-9228-AC8680119E31}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3D7C42-F8EF-4DB1-86CD-6AEACF173EA9}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3666736F-3681-40AF-8649-4D01FC65C270}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C92147-1B62-47FD-A17E-09D4C5C8D3F3}"/>
 </file>